--- a/Risikolog.xlsx
+++ b/Risikolog.xlsx
@@ -333,7 +333,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="21.3"/>
@@ -406,14 +406,14 @@
         <v>12</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="n">
         <f aca="false">H3*I3</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Risikolog.xlsx
+++ b/Risikolog.xlsx
@@ -406,14 +406,14 @@
         <v>12</v>
       </c>
       <c r="H3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="J3" s="2" t="n">
         <f aca="false">H3*I3</f>
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
